--- a/src/main/resources/excel_data/ConveyorBulkUpload3.xlsx
+++ b/src/main/resources/excel_data/ConveyorBulkUpload3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishmitha G\Downloads\ctp-contiplus-web-qa-automation-java\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Supreetha\Documents\Automation\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F836109-E022-4918-9B4E-72B153CC9F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB0F168-4CFA-4058-84C2-898B34E46F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,9 +440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -480,7 +480,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -586,7 +586,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -728,7 +728,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/src/main/resources/excel_data/ConveyorBulkUpload3.xlsx
+++ b/src/main/resources/excel_data/ConveyorBulkUpload3.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Supreetha\Documents\Automation\ctp-contiplus-web-qa-automation-java\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ostan/Documents/Automation/ctp-contiplus-web-qa-automation-java_ostan/ctp-contiplus-web-qa-automation-java/src/main/resources/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB0F168-4CFA-4058-84C2-898B34E46F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD042CE-CE2B-4541-9220-58863B927F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Master" sheetId="1" r:id="rId1"/>
+    <sheet name="Cust Automation Sanity Site Aus" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -737,15 +737,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH42"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="19.19921875" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
     <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="19.796875" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +849,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -953,7 +953,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>64</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>77</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>79</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>80</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>81</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>82</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>83</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>84</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>85</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>86</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>87</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>88</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>89</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>90</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>91</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>92</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>93</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>94</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>95</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>96</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>97</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>98</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>99</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>100</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>101</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>102</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>103</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>104</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>107</v>
       </c>
@@ -4217,7 +4217,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>108</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>110</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>111</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>112</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>113</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>114</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>44555</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:34" ht="68" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>115</v>
       </c>
